--- a/artfynd/A 52510-2022 artfynd.xlsx
+++ b/artfynd/A 52510-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52510-2022 artfynd.xlsx
+++ b/artfynd/A 52510-2022 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104739477</v>
+        <v>104739480</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510438.2264967927</v>
+        <v>510439</v>
       </c>
       <c r="R2" t="n">
-        <v>6691185.266260283</v>
+        <v>6691184</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104739480</v>
+        <v>104739477</v>
       </c>
       <c r="B3" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510439.7162869184</v>
+        <v>510438</v>
       </c>
       <c r="R3" t="n">
-        <v>6691184.280859434</v>
+        <v>6691185</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 52510-2022 artfynd.xlsx
+++ b/artfynd/A 52510-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104739480</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,8 +896,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104739477</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>